--- a/data/P2/P2T2_BQ4.xlsx
+++ b/data/P2/P2T2_BQ4.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9577E56E-7D6E-324F-B2F4-09722F3A88C0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A9A3FA-0917-E34E-A30C-DB8A6C8F20A0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="460" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="30680" yWindow="3840" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -219,13 +220,137 @@
   <si>
     <t>有責任的；
 負責的</t>
+  </si>
+  <si>
+    <t>The Earth gives us special and important things that we need to help us live.</t>
+  </si>
+  <si>
+    <t>地球給我們特別又重要的東西，幫助我們生存。</t>
+  </si>
+  <si>
+    <t>We call these things natural resources.</t>
+  </si>
+  <si>
+    <r>
+      <t>我們稱這些東西為</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>天然資源</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <t>Living things need clean air to breathe and clean water to drink.</t>
+  </si>
+  <si>
+    <t>生物需要乾淨的空氣來呼吸，乾淨的水來飲用。</t>
+  </si>
+  <si>
+    <t>Plants need sunlight and land to grow, and we need plants for food.</t>
+  </si>
+  <si>
+    <t>植物需要陽光和土地生長，而我們需要植物作為食物。</t>
+  </si>
+  <si>
+    <t>When plants breathe, they clean the air around them.</t>
+  </si>
+  <si>
+    <t>植物呼吸時，會淨化周圍的空氣。</t>
+  </si>
+  <si>
+    <t>We use the wood from plants and trees to make a lot of things, like paper, some houses, and furniture.</t>
+  </si>
+  <si>
+    <t>我們使用植物和樹木的木材製作很多東西，例如紙、部分房屋和家具。</t>
+  </si>
+  <si>
+    <t>Smoke from cars and factories makes the air dirty.</t>
+  </si>
+  <si>
+    <t>汽車和工廠的煙霧會讓空氣變髒。</t>
+  </si>
+  <si>
+    <t>People can get sick and plants can't grow.</t>
+  </si>
+  <si>
+    <t>人們會生病，植物也無法生長。</t>
+  </si>
+  <si>
+    <t>Trash is very bad for our natural resources.</t>
+  </si>
+  <si>
+    <t>垃圾對我們的天然資源非常有害。</t>
+  </si>
+  <si>
+    <t>It goes to places called landfills, and it stays there forever.</t>
+  </si>
+  <si>
+    <r>
+      <t>垃圾會被送到叫做</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>垃圾掩埋場</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的地方，並永遠留在那裡。</t>
+    </r>
+  </si>
+  <si>
+    <t>They smell bad, and farmers can't grow food on it.</t>
+  </si>
+  <si>
+    <t>那裡氣味難聞，農夫也無法在上面種植食物。</t>
+  </si>
+  <si>
+    <t>sentence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chinese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -253,6 +378,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -276,7 +410,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -291,6 +425,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -954,4 +1091,114 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{171F42B4-4828-C743-9A62-B0C684B7B24B}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="88.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/P2/P2T2_BQ4.xlsx
+++ b/data/P2/P2T2_BQ4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A9A3FA-0917-E34E-A30C-DB8A6C8F20A0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3A58DD-3F78-7D42-B56E-40AB051715C4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30680" yWindow="3840" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="30680" yWindow="3840" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="144">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -343,6 +343,179 @@
   </si>
   <si>
     <t>chinese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/ˈenədʒi/</t>
+  </si>
+  <si>
+    <t>en-er-gy</t>
+  </si>
+  <si>
+    <t>/ˈfjuːəl/</t>
+  </si>
+  <si>
+    <t>fu-el</t>
+  </si>
+  <si>
+    <t>/ˈneɪtʃə(r)/</t>
+  </si>
+  <si>
+    <t>na-ture</t>
+  </si>
+  <si>
+    <t>/ɪnˈvaɪrənmənt/</t>
+  </si>
+  <si>
+    <t>en-vi-ron-ment</t>
+  </si>
+  <si>
+    <t>/ˌriːˈjuːz/</t>
+  </si>
+  <si>
+    <t>re-use</t>
+  </si>
+  <si>
+    <t>/rɪˈdjuːs/</t>
+  </si>
+  <si>
+    <t>re-duce</t>
+  </si>
+  <si>
+    <t>/ˌriːˈsaɪkl/</t>
+  </si>
+  <si>
+    <t>re-cy-cle</t>
+  </si>
+  <si>
+    <t>/kənˈsɜːv/</t>
+  </si>
+  <si>
+    <t>con-serve</t>
+  </si>
+  <si>
+    <t>/ˈkɒmpɒst/</t>
+  </si>
+  <si>
+    <t>com-post</t>
+  </si>
+  <si>
+    <t>/fuːd weɪst/</t>
+  </si>
+  <si>
+    <t>/məˈʃiːn/</t>
+  </si>
+  <si>
+    <t>ma-chine</t>
+  </si>
+  <si>
+    <t>/kʌt daʊn/</t>
+  </si>
+  <si>
+    <t>/juːst ʌp/</t>
+  </si>
+  <si>
+    <t>/ɪˈnʌf/</t>
+  </si>
+  <si>
+    <t>e-nough</t>
+  </si>
+  <si>
+    <t>/riːˈsaɪklɪŋ plɑːnt/</t>
+  </si>
+  <si>
+    <t>re-cy-cling plant</t>
+  </si>
+  <si>
+    <t>/pəˈluːʃn/</t>
+  </si>
+  <si>
+    <t>pol-lu-tion</t>
+  </si>
+  <si>
+    <t>/ˈlɪtə(r)/</t>
+  </si>
+  <si>
+    <t>lit-ter</t>
+  </si>
+  <si>
+    <t>/ˈplæstɪk/</t>
+  </si>
+  <si>
+    <t>plas-tic</t>
+  </si>
+  <si>
+    <t>/ˈpækɪdʒɪŋ/</t>
+  </si>
+  <si>
+    <t>pack-ag-ing</t>
+  </si>
+  <si>
+    <t>/ˈsɪŋɡl juːz ˈaɪtəmz /dɪˈspəʊzəbl ˈaɪtəmz/</t>
+  </si>
+  <si>
+    <t>sin-gle use i-tems / dis-pos-a-ble i-tems</t>
+  </si>
+  <si>
+    <t>/tɜːn ɒf/</t>
+  </si>
+  <si>
+    <t>/prəˈtekt/</t>
+  </si>
+  <si>
+    <t>pro-tect</t>
+  </si>
+  <si>
+    <t>/teɪk keə ɒv/</t>
+  </si>
+  <si>
+    <t>/ˈreskjuː/</t>
+  </si>
+  <si>
+    <t>res-cue</t>
+  </si>
+  <si>
+    <t>/dəʊˈneɪʃn/</t>
+  </si>
+  <si>
+    <t>do-na-tion</t>
+  </si>
+  <si>
+    <t>/ɪmˈpɔːtnt/</t>
+  </si>
+  <si>
+    <t>im-por-tant</t>
+  </si>
+  <si>
+    <t>/ˈspeʃl/</t>
+  </si>
+  <si>
+    <t>spe-cial</t>
+  </si>
+  <si>
+    <t>/ˈwʌndəfl/</t>
+  </si>
+  <si>
+    <t>won-der-ful</t>
+  </si>
+  <si>
+    <t>/ˈθɔːtfl/</t>
+  </si>
+  <si>
+    <t>thought-ful</t>
+  </si>
+  <si>
+    <t>/rɪˈspɒnsəbl/</t>
+  </si>
+  <si>
+    <t>res-pon-si-ble</t>
+  </si>
+  <si>
+    <t>phonetics</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>syllable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -743,10 +916,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -756,8 +934,17 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -767,8 +954,14 @@
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -778,8 +971,14 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -789,8 +988,14 @@
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -800,8 +1005,14 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -811,8 +1022,14 @@
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -822,8 +1039,14 @@
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -833,8 +1056,14 @@
       <c r="C8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -844,8 +1073,14 @@
       <c r="C9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -855,8 +1090,14 @@
       <c r="C10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -866,8 +1107,14 @@
       <c r="C11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -877,8 +1124,14 @@
       <c r="C12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -888,8 +1141,14 @@
       <c r="C13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -899,8 +1158,14 @@
       <c r="C14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -910,8 +1175,14 @@
       <c r="C15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -921,8 +1192,14 @@
       <c r="C16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -932,8 +1209,14 @@
       <c r="C17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -943,8 +1226,14 @@
       <c r="C18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -954,8 +1243,14 @@
       <c r="C19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -965,8 +1260,14 @@
       <c r="C20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="60">
+      <c r="D20" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="60">
       <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
@@ -976,8 +1277,14 @@
       <c r="C21">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -987,8 +1294,14 @@
       <c r="C22">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" t="s">
+        <v>124</v>
+      </c>
+      <c r="E22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -998,8 +1311,14 @@
       <c r="C23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -1009,8 +1328,14 @@
       <c r="C24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" t="s">
+        <v>127</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -1020,8 +1345,14 @@
       <c r="C25">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -1031,8 +1362,14 @@
       <c r="C26">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -1042,8 +1379,14 @@
       <c r="C27">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -1053,8 +1396,14 @@
       <c r="C28">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -1064,8 +1413,14 @@
       <c r="C29">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
@@ -1075,8 +1430,14 @@
       <c r="C30">
         <v>6</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="28">
+      <c r="D30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="28">
       <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
@@ -1085,6 +1446,12 @@
       </c>
       <c r="C31">
         <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/data/P2/P2T2_BQ4.xlsx
+++ b/data/P2/P2T2_BQ4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/English/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3A58DD-3F78-7D42-B56E-40AB051715C4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50529364-4F10-9746-8947-2BEC65D475B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30680" yWindow="3840" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="29220" yWindow="2160" windowWidth="29120" windowHeight="18480" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="175">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -95,10 +95,6 @@
   </si>
   <si>
     <t>packaging</t>
-  </si>
-  <si>
-    <t>single use items
-(disposable items)</t>
   </si>
   <si>
     <t>turn off</t>
@@ -451,12 +447,6 @@
     <t>pack-ag-ing</t>
   </si>
   <si>
-    <t>/ˈsɪŋɡl juːz ˈaɪtəmz /dɪˈspəʊzəbl ˈaɪtəmz/</t>
-  </si>
-  <si>
-    <t>sin-gle use i-tems / dis-pos-a-ble i-tems</t>
-  </si>
-  <si>
     <t>/tɜːn ɒf/</t>
   </si>
   <si>
@@ -517,13 +507,151 @@
   <si>
     <t>syllable</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>single use items</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ˈsɪŋɡl juːz ˈaɪt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ə</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>mz /</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sin-gle use i-tems</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>English explanation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power to make machines, cars and lights work</t>
+  </si>
+  <si>
+    <t>Things like oil or gas that give cars energy to move</t>
+  </si>
+  <si>
+    <t>All trees, animals, rivers and mountains around us</t>
+  </si>
+  <si>
+    <t>The air, water and land where all living things live</t>
+  </si>
+  <si>
+    <t>Use the same thing again instead of throwing it away</t>
+  </si>
+  <si>
+    <t>Use less of something to make less waste</t>
+  </si>
+  <si>
+    <t>Turn old used things into new items</t>
+  </si>
+  <si>
+    <t>Save water, energy or things so we do not waste them</t>
+  </si>
+  <si>
+    <t>Rotten food waste that becomes good soil for plants</t>
+  </si>
+  <si>
+    <t>Food we do not eat and throw away</t>
+  </si>
+  <si>
+    <t>A tool that uses energy to do work for us</t>
+  </si>
+  <si>
+    <t>Chop trees so they fall to the ground</t>
+  </si>
+  <si>
+    <t>There is none left after we finish using it</t>
+  </si>
+  <si>
+    <t>We have as much as we need</t>
+  </si>
+  <si>
+    <t>A place that changes old rubbish into new things</t>
+  </si>
+  <si>
+    <t>Dirty air, water or land that harms nature</t>
+  </si>
+  <si>
+    <t>Rubbish people drop on the ground or in water</t>
+  </si>
+  <si>
+    <t>A man-made material for bottles, bags and toys</t>
+  </si>
+  <si>
+    <t>Wrappers or boxes around food and toys</t>
+  </si>
+  <si>
+    <t>Things we use once and then throw away</t>
+  </si>
+  <si>
+    <t>Stop lights, taps or machines from working</t>
+  </si>
+  <si>
+    <t>Keep nature, animals and people safe from harm</t>
+  </si>
+  <si>
+    <t>Look after something or someone well</t>
+  </si>
+  <si>
+    <t>Save animals or people from danger</t>
+  </si>
+  <si>
+    <t>Things or money we give to help others</t>
+  </si>
+  <si>
+    <t>Something we must care about very much</t>
+  </si>
+  <si>
+    <t>Not usual, unique and different from others</t>
+  </si>
+  <si>
+    <t>Very nice and makes you feel happy</t>
+  </si>
+  <si>
+    <t>Kind and thinking about other people’s needs</t>
+  </si>
+  <si>
+    <t>Know what good things to do and do them well</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -559,6 +687,20 @@
       <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="PMingLiU"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -920,8 +1062,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -935,10 +1077,13 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E1" t="s">
-        <v>143</v>
+        <v>140</v>
+      </c>
+      <c r="F1" t="s">
+        <v>144</v>
       </c>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -949,16 +1094,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" t="s">
         <v>87</v>
       </c>
-      <c r="E2" t="s">
-        <v>88</v>
+      <c r="F2" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -966,16 +1114,19 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" t="s">
         <v>89</v>
       </c>
-      <c r="E3" t="s">
-        <v>90</v>
+      <c r="F3" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -983,16 +1134,19 @@
         <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" t="s">
         <v>91</v>
       </c>
-      <c r="E4" t="s">
-        <v>92</v>
+      <c r="F4" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1000,16 +1154,19 @@
         <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" t="s">
         <v>93</v>
       </c>
-      <c r="E5" t="s">
-        <v>94</v>
+      <c r="F5" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1017,16 +1174,19 @@
         <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
         <v>95</v>
       </c>
-      <c r="E6" t="s">
-        <v>96</v>
+      <c r="F6" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1034,16 +1194,19 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
         <v>97</v>
       </c>
-      <c r="E7" t="s">
-        <v>98</v>
+      <c r="F7" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1051,16 +1214,19 @@
         <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
         <v>99</v>
       </c>
-      <c r="E8" t="s">
-        <v>100</v>
+      <c r="F8" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1068,16 +1234,19 @@
         <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" t="s">
         <v>101</v>
       </c>
-      <c r="E9" t="s">
-        <v>102</v>
+      <c r="F9" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1085,16 +1254,19 @@
         <v>11</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" t="s">
         <v>103</v>
       </c>
-      <c r="E10" t="s">
-        <v>104</v>
+      <c r="F10" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1102,16 +1274,19 @@
         <v>12</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1119,16 +1294,19 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" t="s">
         <v>106</v>
       </c>
-      <c r="E12" t="s">
-        <v>107</v>
+      <c r="F12" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1136,16 +1314,19 @@
         <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1153,16 +1334,19 @@
         <v>15</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
+      </c>
+      <c r="F14" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1170,16 +1354,19 @@
         <v>16</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
         <v>110</v>
       </c>
-      <c r="E15" t="s">
-        <v>111</v>
+      <c r="F15" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1187,271 +1374,319 @@
         <v>17</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
         <v>112</v>
       </c>
-      <c r="E16" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17">
         <v>4</v>
       </c>
       <c r="D17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" t="s">
         <v>114</v>
       </c>
-      <c r="E17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18">
         <v>4</v>
       </c>
       <c r="D18" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" t="s">
         <v>116</v>
       </c>
-      <c r="E18" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19">
         <v>4</v>
       </c>
       <c r="D19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" t="s">
         <v>118</v>
       </c>
-      <c r="E19" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C20">
         <v>4</v>
       </c>
       <c r="D20" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" t="s">
         <v>120</v>
       </c>
-      <c r="E20" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="60">
+      <c r="F20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30">
       <c r="A21" s="2" t="s">
-        <v>22</v>
+        <v>141</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21">
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="E21" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>143</v>
+      </c>
+      <c r="F21" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C22">
         <v>5</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="B23" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23">
         <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E23" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>123</v>
+      </c>
+      <c r="F23" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C24">
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="B25" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C25">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E25" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>126</v>
+      </c>
+      <c r="F25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C26">
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E26" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>128</v>
+      </c>
+      <c r="F26" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C27">
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E27" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>130</v>
+      </c>
+      <c r="F27" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C28">
         <v>6</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E28" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>132</v>
+      </c>
+      <c r="F28" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C29">
         <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>134</v>
+      </c>
+      <c r="F29" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C30">
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E30" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="28">
+        <v>136</v>
+      </c>
+      <c r="F30" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="28">
       <c r="A31" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31">
         <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E31" t="s">
-        <v>141</v>
+        <v>138</v>
+      </c>
+      <c r="F31" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -1470,98 +1705,98 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
         <v>63</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
         <v>65</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" t="s">
         <v>67</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
         <v>69</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
         <v>71</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" t="s">
         <v>73</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" t="s">
         <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
         <v>77</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
         <v>79</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
         <v>81</v>
-      </c>
-      <c r="B11" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" t="s">
         <v>83</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
